--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.69456455536486</v>
+        <v>5.475366740246789</v>
       </c>
       <c r="D2" t="n">
-        <v>33.6207141663612</v>
+        <v>5.463366052033694</v>
       </c>
       <c r="E2" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F2" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.51047098721462</v>
+        <v>4.795451535422377</v>
       </c>
       <c r="D3" t="n">
-        <v>26.66393970167645</v>
+        <v>4.332890201522424</v>
       </c>
       <c r="E3" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F3" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.6034524719736</v>
+        <v>1.88556102669571</v>
       </c>
       <c r="D4" t="n">
-        <v>9.928834944240551</v>
+        <v>1.61343567843909</v>
       </c>
       <c r="E4" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F4" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.942737870476796</v>
+        <v>1.290694903952479</v>
       </c>
       <c r="D5" t="n">
-        <v>5.084221985177584</v>
+        <v>0.8261860725913575</v>
       </c>
       <c r="E5" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F5" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.301559647007825</v>
+        <v>1.024003442638772</v>
       </c>
       <c r="D6" t="n">
-        <v>7.562792958941383</v>
+        <v>1.228953855827975</v>
       </c>
       <c r="E6" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F6" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.76556798289951</v>
+        <v>2.72440479722117</v>
       </c>
       <c r="D7" t="n">
-        <v>16.29789513472401</v>
+        <v>2.648407959392651</v>
       </c>
       <c r="E7" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F7" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.79318311375447</v>
+        <v>4.678892255985102</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62167917089873</v>
+        <v>4.651022865271043</v>
       </c>
       <c r="E8" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F8" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.12946604584565</v>
+        <v>5.383538232449919</v>
       </c>
       <c r="D9" t="n">
-        <v>22.71030794336857</v>
+        <v>3.690425040797392</v>
       </c>
       <c r="E9" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F9" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.70563149641158</v>
+        <v>5.152165118166883</v>
       </c>
       <c r="D10" t="n">
-        <v>20.65724940129934</v>
+        <v>3.356803027711142</v>
       </c>
       <c r="E10" t="n">
-        <v>10.73252713292087</v>
+        <v>1.744035659099641</v>
       </c>
       <c r="F10" t="n">
-        <v>9.402330634203658</v>
+        <v>1.527878728058095</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
